--- a/artfynd/A 9552-2025 artfynd.xlsx
+++ b/artfynd/A 9552-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136542003</v>
       </c>
       <c r="B2" t="n">
-        <v>99344</v>
+        <v>99347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136542740</v>
       </c>
       <c r="B3" t="n">
-        <v>99344</v>
+        <v>99347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136546509</v>
       </c>
       <c r="B4" t="n">
-        <v>99344</v>
+        <v>99347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136539813</v>
       </c>
       <c r="B5" t="n">
-        <v>103025</v>
+        <v>103028</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136549243</v>
       </c>
       <c r="B6" t="n">
-        <v>103025</v>
+        <v>103028</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 9552-2025 artfynd.xlsx
+++ b/artfynd/A 9552-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136542003</v>
       </c>
       <c r="B2" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136542740</v>
       </c>
       <c r="B3" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136546509</v>
       </c>
       <c r="B4" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136539813</v>
       </c>
       <c r="B5" t="n">
-        <v>103028</v>
+        <v>103029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136549243</v>
       </c>
       <c r="B6" t="n">
-        <v>103028</v>
+        <v>103029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 9552-2025 artfynd.xlsx
+++ b/artfynd/A 9552-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136542003</v>
       </c>
       <c r="B2" t="n">
-        <v>99348</v>
+        <v>99353</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136542740</v>
       </c>
       <c r="B3" t="n">
-        <v>99348</v>
+        <v>99353</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136546509</v>
       </c>
       <c r="B4" t="n">
-        <v>99348</v>
+        <v>99353</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136539813</v>
       </c>
       <c r="B5" t="n">
-        <v>103029</v>
+        <v>103034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136549243</v>
       </c>
       <c r="B6" t="n">
-        <v>103029</v>
+        <v>103034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 9552-2025 artfynd.xlsx
+++ b/artfynd/A 9552-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136542003</v>
       </c>
       <c r="B2" t="n">
-        <v>99353</v>
+        <v>99355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136542740</v>
       </c>
       <c r="B3" t="n">
-        <v>99353</v>
+        <v>99355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136546509</v>
       </c>
       <c r="B4" t="n">
-        <v>99353</v>
+        <v>99355</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136539813</v>
       </c>
       <c r="B5" t="n">
-        <v>103034</v>
+        <v>103036</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136549243</v>
       </c>
       <c r="B6" t="n">
-        <v>103034</v>
+        <v>103036</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 9552-2025 artfynd.xlsx
+++ b/artfynd/A 9552-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136542003</v>
       </c>
       <c r="B2" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136542740</v>
       </c>
       <c r="B3" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136546509</v>
       </c>
       <c r="B4" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136539813</v>
       </c>
       <c r="B5" t="n">
-        <v>103036</v>
+        <v>103042</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136549243</v>
       </c>
       <c r="B6" t="n">
-        <v>103036</v>
+        <v>103042</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 9552-2025 artfynd.xlsx
+++ b/artfynd/A 9552-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136542003</v>
       </c>
       <c r="B2" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136542740</v>
       </c>
       <c r="B3" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136546509</v>
       </c>
       <c r="B4" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136539813</v>
       </c>
       <c r="B5" t="n">
-        <v>103042</v>
+        <v>103044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136549243</v>
       </c>
       <c r="B6" t="n">
-        <v>103042</v>
+        <v>103044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 9552-2025 artfynd.xlsx
+++ b/artfynd/A 9552-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136542003</v>
       </c>
       <c r="B2" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136542740</v>
       </c>
       <c r="B3" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136546509</v>
       </c>
       <c r="B4" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136539813</v>
       </c>
       <c r="B5" t="n">
-        <v>103044</v>
+        <v>103045</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136549243</v>
       </c>
       <c r="B6" t="n">
-        <v>103044</v>
+        <v>103045</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 9552-2025 artfynd.xlsx
+++ b/artfynd/A 9552-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136542003</v>
       </c>
       <c r="B2" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136542740</v>
       </c>
       <c r="B3" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136546509</v>
       </c>
       <c r="B4" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136539813</v>
       </c>
       <c r="B5" t="n">
-        <v>103045</v>
+        <v>103051</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136549243</v>
       </c>
       <c r="B6" t="n">
-        <v>103045</v>
+        <v>103051</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 9552-2025 artfynd.xlsx
+++ b/artfynd/A 9552-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136542003</v>
       </c>
       <c r="B2" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136542740</v>
       </c>
       <c r="B3" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136546509</v>
       </c>
       <c r="B4" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136539813</v>
       </c>
       <c r="B5" t="n">
-        <v>103051</v>
+        <v>103055</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136549243</v>
       </c>
       <c r="B6" t="n">
-        <v>103051</v>
+        <v>103055</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 9552-2025 artfynd.xlsx
+++ b/artfynd/A 9552-2025 artfynd.xlsx
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Mikael Andersson</t>
+          <t>Mikael Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 9552-2025 artfynd.xlsx
+++ b/artfynd/A 9552-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136542003</v>
       </c>
       <c r="B2" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136542740</v>
       </c>
       <c r="B3" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136546509</v>
       </c>
       <c r="B4" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mikael Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1001,7 +1001,7 @@
         <v>136539813</v>
       </c>
       <c r="B5" t="n">
-        <v>103055</v>
+        <v>103057</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136549243</v>
       </c>
       <c r="B6" t="n">
-        <v>103055</v>
+        <v>103057</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 9552-2025 artfynd.xlsx
+++ b/artfynd/A 9552-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136542003</v>
       </c>
       <c r="B2" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136542740</v>
       </c>
       <c r="B3" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136546509</v>
       </c>
       <c r="B4" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136539813</v>
       </c>
       <c r="B5" t="n">
-        <v>103057</v>
+        <v>103059</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136549243</v>
       </c>
       <c r="B6" t="n">
-        <v>103057</v>
+        <v>103059</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 9552-2025 artfynd.xlsx
+++ b/artfynd/A 9552-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136542003</v>
       </c>
       <c r="B2" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136542740</v>
       </c>
       <c r="B3" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136546509</v>
       </c>
       <c r="B4" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136539813</v>
       </c>
       <c r="B5" t="n">
-        <v>103059</v>
+        <v>103072</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136549243</v>
       </c>
       <c r="B6" t="n">
-        <v>103059</v>
+        <v>103072</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 9552-2025 artfynd.xlsx
+++ b/artfynd/A 9552-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136542003</v>
       </c>
       <c r="B2" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136542740</v>
       </c>
       <c r="B3" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136546509</v>
       </c>
       <c r="B4" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136539813</v>
       </c>
       <c r="B5" t="n">
-        <v>103072</v>
+        <v>103074</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136549243</v>
       </c>
       <c r="B6" t="n">
-        <v>103072</v>
+        <v>103074</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
